--- a/upload/pytest-temp/test_comparison_excel_does_not0/comparison.xlsx
+++ b/upload/pytest-temp/test_comparison_excel_does_not0/comparison.xlsx
@@ -529,7 +529,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Дата расчёта: 14.09.2026 14:04</t>
+          <t>Дата расчёта: 14.09.2026 14:11</t>
         </is>
       </c>
     </row>

--- a/upload/pytest-temp/test_comparison_excel_does_not0/comparison.xlsx
+++ b/upload/pytest-temp/test_comparison_excel_does_not0/comparison.xlsx
@@ -529,7 +529,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Дата расчёта: 14.09.2026 14:11</t>
+          <t>Дата расчёта: 14.09.2026 14:19</t>
         </is>
       </c>
     </row>

--- a/upload/pytest-temp/test_comparison_excel_does_not0/comparison.xlsx
+++ b/upload/pytest-temp/test_comparison_excel_does_not0/comparison.xlsx
@@ -529,7 +529,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Дата расчёта: 14.09.2026 14:19</t>
+          <t>Дата расчёта: 14.09.2026 14:21</t>
         </is>
       </c>
     </row>

--- a/upload/pytest-temp/test_comparison_excel_does_not0/comparison.xlsx
+++ b/upload/pytest-temp/test_comparison_excel_does_not0/comparison.xlsx
@@ -529,7 +529,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Дата расчёта: 14.09.2026 14:21</t>
+          <t>Дата расчёта: 14.09.2026 14:27</t>
         </is>
       </c>
     </row>

--- a/upload/pytest-temp/test_comparison_excel_does_not0/comparison.xlsx
+++ b/upload/pytest-temp/test_comparison_excel_does_not0/comparison.xlsx
@@ -529,7 +529,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Дата расчёта: 14.09.2026 14:34</t>
+          <t>Дата расчёта: 14.09.2026 15:16</t>
         </is>
       </c>
     </row>

--- a/upload/pytest-temp/test_comparison_excel_does_not0/comparison.xlsx
+++ b/upload/pytest-temp/test_comparison_excel_does_not0/comparison.xlsx
@@ -529,7 +529,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Дата расчёта: 14.09.2026 15:16</t>
+          <t>Дата расчёта: 14.09.2026 15:19</t>
         </is>
       </c>
     </row>

--- a/upload/pytest-temp/test_comparison_excel_does_not0/comparison.xlsx
+++ b/upload/pytest-temp/test_comparison_excel_does_not0/comparison.xlsx
@@ -529,7 +529,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Дата расчёта: 14.09.2026 16:49</t>
+          <t>Дата расчёта: 14.09.2026 17:09</t>
         </is>
       </c>
     </row>
